--- a/artfynd/A 15177-2024 artfynd.xlsx
+++ b/artfynd/A 15177-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113367362</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3049837</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3050291</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,8 +1132,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113367370</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 15177-2024 artfynd.xlsx
+++ b/artfynd/A 15177-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>3049837</v>
       </c>
       <c r="B3" t="n">
-        <v>99118</v>
+        <v>99242</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>3050291</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>99242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15177-2024 artfynd.xlsx
+++ b/artfynd/A 15177-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>3049837</v>
       </c>
       <c r="B3" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>3050291</v>
       </c>
       <c r="B4" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15177-2024 artfynd.xlsx
+++ b/artfynd/A 15177-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113367370</v>
+        <v>3049837</v>
       </c>
       <c r="B3" t="n">
-        <v>99118</v>
+        <v>99274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,24 +812,29 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Madhagen, Sm</t>
+          <t>vetlanda ca 1 km väster om karlslund, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502917</v>
+        <v>503116</v>
       </c>
       <c r="R3" t="n">
-        <v>6365600</v>
+        <v>6365355</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2011-08-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2011-08-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,19 +878,261 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jakob Wilhelmsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jakob Wilhelmsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3049837</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3050291</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>vetlanda 1 km väster om karlslund, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>503200</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6365835</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2011-08-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2011-08-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>utbrett ca 50m radie</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Gran-Tallskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jakob Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jakob Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3050291</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113367370</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Madhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>502917</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6365600</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-11-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-11-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/113367370</t>
         </is>
@@ -895,6 +1142,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15177-2024 artfynd.xlsx
+++ b/artfynd/A 15177-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>3049837</v>
       </c>
       <c r="B3" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>3050291</v>
       </c>
       <c r="B4" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15177-2024 artfynd.xlsx
+++ b/artfynd/A 15177-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>3049837</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>3050291</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15177-2024 artfynd.xlsx
+++ b/artfynd/A 15177-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>3049837</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>3050291</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15177-2024 artfynd.xlsx
+++ b/artfynd/A 15177-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>3049837</v>
       </c>
       <c r="B3" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>3050291</v>
       </c>
       <c r="B4" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15177-2024 artfynd.xlsx
+++ b/artfynd/A 15177-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>3049837</v>
       </c>
       <c r="B3" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>3050291</v>
       </c>
       <c r="B4" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
